--- a/output/distributable_register.xlsx
+++ b/output/distributable_register.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distributable Register" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Distributable Register'!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Distributable Register'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -138,6 +138,211 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -427,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -446,8 +651,65 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="115" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DDD52MN3XCB6YBD7</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="115" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>JBOA6DY5HEVS5VAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="115" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VI5NAR2U7UJUQ75P</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="115" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>G7KKZQVFT5RSEXLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="115" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CCX2QDL6IJJ3SCRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="115" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EVNPVZZ4PINRHY3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="115" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B5J6XXJHV3RQQQWH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="115" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5LEPA4HRFWDM47M4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1"/>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>